--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -21,6 +21,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyEffects" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordingFixes" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PartySkillBounds" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JointEffects" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JointSkillSentences" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,6 +616,30 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>Upper bound of each party skill bonus (DT2-2 wiki), in the order the sentence names them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JointEffects</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Joint skills: how the value of an effect is written when a sentence quotes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JointSkillSentences</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Joint skills: the sentence of the game with the stored value of an effect in place of {eID}. A skill without a row keeps its text.</t>
         </is>
       </c>
     </row>
@@ -2291,6 +2317,923 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Effect_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Style</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Paralysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Silence</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stun</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Instakill</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Petrification</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Shadow Sew</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>54</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Turn delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>161</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>signed_pct</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Physical attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>162</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>signed_pct</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Physical defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>163</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>signed_pct</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Magic defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>166</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>signed_pct</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Physical accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>168</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>signed_pct</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>173</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>signed_pct</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Magic attack. Named by the game table; unit by analogy with 161</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>174</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>signed_points_pct</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Crit rate. Named by the game table; unit by analogy with 31 (points)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>169</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>signed_points_pct</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>All resistances, in points (one point is 1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>66</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>signed_num</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pep UP. Named by the game table; 80 (Pep DOWN) is stored the same way</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>105</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HP on revival, fraction of max HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>433</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Money Loss: fraction of the gold held (DT2-2 wiki: 5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>296</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Damage cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>147</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Turns a summoned attack lasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>93</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Hit count</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>88</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>times</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1 + value: God Punch says "2x damage" for a stored 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>89</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Game table: 2~5 Hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>94</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Game table: 0~4 Hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>95</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Game table: 1~5 Hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>96</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Game table: 3~5 Hits</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Catastrophe</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inflict a powerful physical attack on one enemy. Inflicts slow ({e122}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Genocide Rain</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rain arrows down upon all enemies across {e147} turns.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Wiki: 2 volleys, each attacks every enemy twice a turn for 4 turns</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Divine Punishment!</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Deal physical damage to an enemy row. {e119} chance of instakill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nightmare Fall</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Deal non-elemental damage to all enemies. {e116} chance of causing sleep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Powered-Up Beatdown!</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inflict one enemy with {e96} bash attacks. {e118} chance of stun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Psychowave</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Deal non-elemental damage and lower DEF and magic defense ({e162}) for all enemies.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The original names DEF only; the data also lowers magic defense (163), as the Japanese text says</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avatara</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deal physical damage and {e95} defense-piercing attacks on one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gjallarhorn</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Activate Circle Brave ({e161}), Circle Protect ({e162}) and Moon Curtain ({e169}) at once.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Shortened ("all at the same time") to make room</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Suppression Arrow</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Deal damage with an {e117} chance to silence/freeze. Pierces to the back row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rapid Storm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Form up to increase speed ({e168}) and physical accuracy ({e166}) for all allies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Evolution</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Increase magic attack ({e173}) and critical rate ({e174}) for all allies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bunker Buster</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Deal damage and reduce physical attack/defense ({e161}). Pierces to the back row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Paralyzing Wind</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Inflict a wind attack against all enemies. {e115} chance of paralysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Daruma-Drop!</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Deal physical damage, with a {e54} chance to delay the target's next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Testament</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Deal physical damage and use Shadow Sew ({e123}) against an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brain Burst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Deal physical damage to one enemy. {e113} chance of poison/paralysis/sleep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Happy Banquet</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Increase Pep ({e66}) for the ally whose Pep is the lowest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hysteric Slap</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Inflict {e94} bash attacks on an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fire of Purgatory</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Attack one enemy ({e88} damage to Undead, Demons, and Apparitions).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Same effect and value as God Punch, which says "2x damage"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Curse Bullet</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Waste one enemy and poison the target ({e113}) with a rare gun-type weapon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Beast Blitz</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rough up ({e93} hits) and poison ({e113}) one enemy with the power of darkness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Durchbruch</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fire two arrows of light that pierce to the back row and may silence ({e117}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Maid Beam</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The deadly Maid Beam pierces to the back row and begins petrifying targets ({e120}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Feuerkraft</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Immolate all enemies and absorb their HP and TP (damage cap {e296}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gold Power</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hurl {e433} of your wallet at one enemy for up to {e296} damage. (You won't get it back.)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>777 Fever</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dish out paralysis ({e115}) and 7 times the user's level in damage to all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Apocrypha</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Waste one enemy and lower target's phys. DEF ({e162}) with a rare gun-type weapon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Anastasia</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Summon the goddess of life to resurrect all allies (HP {e105}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lots Of Guns</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>With three firearms in your hands, rain lead upon your enemies at random ({e93} hits).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -20,9 +20,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemEffects" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyEffects" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WordingFixes" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PartySkillBounds" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JointEffects" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JointSkillSentences" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JointEffects" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JointSkillSentences" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueSkillNotes" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PartySkillBounds" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -531,7 +532,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Line 1 of skills with several figures: {0}, {1} are the figures of the labels listed, {dmg} the damage word.</t>
+          <t>Line 1 of skills with several figures: {0}, {1} are the figures of the labels listed, {dmg} the damage word. Figures = values: used only when Settings/line1_values is yes. Figures = chances: always used.</t>
         </is>
       </c>
     </row>
@@ -615,7 +616,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Upper bound of each party skill bonus (DT2-2 wiki), in the order the sentence names them.</t>
+          <t>Party skills: the effect line shown, with the upper bound of each bonus (DT2-2 wiki). Bounds lists the figures the sentence must carry. An empty sentence keeps the text of the game.</t>
         </is>
       </c>
     </row>
@@ -640,6 +641,18 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>Joint skills: the sentence of the game with the stored value of an effect in place of {eID}. A skill without a row keeps its text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UniqueSkillNotes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Unique skills: a line added under the box for a figure that only a guide gives (it says so).</t>
         </is>
       </c>
     </row>
@@ -1886,13 +1899,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1903,412 +1916,487 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Style</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Bounds</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>360</v>
+        <v>113</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Full of Guts</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>+100</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Poison</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>361</v>
+        <v>114</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vigor Trio</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>+32</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Freeze</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>362</v>
+        <v>115</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kindred Spirits</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>+50, +20%</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Paralysis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>363</v>
+        <v>116</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Veteran Soldiers</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>+25%</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Sleep</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>364</v>
+        <v>117</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Attentive</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>+20</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Silence</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>365</v>
+        <v>118</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Libra Guard</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>+25</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Stun</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>366</v>
+        <v>119</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vagabonds</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>+20</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Instakill</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>367</v>
+        <v>120</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Beyond Human</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>+20%</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Petrification</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>368</v>
+        <v>122</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NegaPosi</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>+50, +50</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>369</v>
+        <v>123</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dark and Light</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>+20</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Shadow Sew</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>370</v>
+        <v>54</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Natural Klutzes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>+20%</t>
+          <t>chance</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Turn delay</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>371</v>
+        <v>161</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eccentrics</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>+32</t>
+          <t>signed_pct</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Physical attack</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>372</v>
+        <v>162</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Flawless Poise</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>+20%, +20%</t>
+          <t>signed_pct</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Physical defense</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>373</v>
+        <v>163</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Celebrities</t>
+          <t>signed_pct</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The wiki gives no figure</t>
+          <t>Magic defense</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>374</v>
+        <v>166</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sales Experience</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>+20%, +10</t>
+          <t>signed_pct</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Physical accuracy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>375</v>
+        <v>168</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Royal Squadron</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>+10%, +20%</t>
+          <t>signed_pct</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Speed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>376</v>
+        <v>173</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Graceful Agers</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>+20%, +50</t>
+          <t>signed_pct</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Magic attack. Named by the game table; unit by analogy with 161</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>377</v>
+        <v>174</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mission Ongoing</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>+10%, +20</t>
+          <t>signed_points_pct</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Crit rate. Named by the game table; unit by analogy with 31 (points)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>415</v>
+        <v>169</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Board Members</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>+20, +20</t>
+          <t>signed_points_pct</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>All resistances, in points (one point is 1%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>405</v>
+        <v>66</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The New Magi</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>+50, +20%</t>
+          <t>signed_num</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>dt22-wiki page 72</t>
+          <t>Pep UP. Named by the game table; 80 (Pep DOWN) is stored the same way</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>105</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HP on revival, fraction of max HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>433</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Money Loss: fraction of the gold held (DT2-2 wiki: 5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>296</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Damage cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>147</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Turns a summoned attack lasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>93</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Hit count</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>88</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>times</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1 + value: God Punch says "2x damage" for a stored 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>89</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Game table: 2~5 Hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>94</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Game table: 0~4 Hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>95</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Game table: 1~5 Hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>96</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3-5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Game table: 3~5 Hits</t>
         </is>
       </c>
     </row>
@@ -2323,504 +2411,498 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Effect_ID</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Style</t>
+          <t>Sentence</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>113</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Catastrophe</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Poison</t>
+          <t>Inflict a powerful physical attack on one enemy. Inflicts slow ({e122}).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>114</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Genocide Rain</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Freeze</t>
+          <t>Rain arrows down upon all enemies across {e147} turns.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Wiki: 2 volleys, each attacks every enemy twice a turn for 4 turns</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>115</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Divine Punishment!</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Paralysis</t>
+          <t>Deal physical damage to an enemy row. {e119} chance of instakill.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>116</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nightmare Fall</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sleep</t>
+          <t>Deal non-elemental damage to all enemies. {e116} chance of sleep.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>117</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Powered-Up Beatdown!</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Silence</t>
+          <t>Inflict one enemy with {e96} bash attacks. {e118} chance of stun.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>118</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Psychowave</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stun</t>
+          <t>Non-elemental damage to all enemies. DEF and magic defense {e162}.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The original names DEF only; the data also lowers magic defense (163), as the Japanese text says</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>119</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avatara</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Instakill</t>
+          <t>Deal physical damage and {e95} defense-piercing attacks on one enemy.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>120</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gjallarhorn</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Petrification</t>
+          <t>Circle Brave ({e161}), Circle Protect ({e162}) and Moon Curtain ({e169}).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Shortened ("all at the same time") to make room</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>122</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Suppression Arrow</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Slow</t>
+          <t>Deal damage through to the back row. {e117} chance to silence/freeze.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>123</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rapid Storm</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Shadow Sew</t>
+          <t>Form up: speed {e168} and physical accuracy {e166} for all allies.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>54</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Evolution</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>chance</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Turn delay</t>
+          <t>Increase magic attack ({e173}) and critical rate ({e174}) for all allies.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>161</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Bunker Buster</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>signed_pct</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Physical attack</t>
+          <t>Deal damage through to the back row. Physical attack/defense {e161}.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>162</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Paralyzing Wind</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>signed_pct</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Physical defense</t>
+          <t>Inflict a wind attack against all enemies. {e115} chance of paralysis.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>163</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Daruma-Drop!</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>signed_pct</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Magic defense</t>
+          <t>Deal physical damage. {e54} chance to delay the target's next turn.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>166</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Testament</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>signed_pct</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Physical accuracy</t>
+          <t>Deal physical damage and use Shadow Sew ({e123}) against an enemy row.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>168</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Brain Burst</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>signed_pct</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Speed</t>
+          <t>Physical damage to one enemy. {e113} chance of poison/paralysis/sleep.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>173</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Happy Banquet</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>signed_pct</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Magic attack. Named by the game table; unit by analogy with 161</t>
+          <t>Increase Pep ({e66}) for the ally whose Pep is the lowest.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>174</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hysteric Slap</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>signed_points_pct</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Crit rate. Named by the game table; unit by analogy with 31 (points)</t>
+          <t>Inflict {e94} bash attacks on an enemy row.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>169</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fire of Purgatory</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>signed_points_pct</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>All resistances, in points (one point is 1%)</t>
+          <t>Attack one enemy ({e88} damage to Undead, Demons, and Apparitions).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Same effect and value as God Punch, which says "2x damage"</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>66</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Curse Bullet</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>signed_num</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Pep UP. Named by the game table; 80 (Pep DOWN) is stored the same way</t>
+          <t>Waste one enemy and poison it ({e113}) with a rare gun.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>105</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Beast Blitz</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pct</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HP on revival, fraction of max HP</t>
+          <t>Rough up ({e93} hits) and poison ({e113}) one enemy with dark power.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>433</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Durchbruch</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pct</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Money Loss: fraction of the gold held (DT2-2 wiki: 5%)</t>
+          <t>Two arrows of light pierce to the back row and may silence ({e117}).</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>296</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Maid Beam</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Damage cap</t>
+          <t>The deadly Maid Beam pierces to the back row. Petrifying ({e120}).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>147</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Feuerkraft</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Turns a summoned attack lasts</t>
+          <t>Immolate all enemies and absorb their HP and TP (damage cap {e296}).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>93</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gold Power</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>num</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Hit count</t>
+          <t>Hurl {e433} of your wallet at one enemy (max {e296} damage). No refunds.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>88</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>777 Fever</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>times</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1 + value: God Punch says "2x damage" for a stored 1</t>
+          <t>Dish out paralysis ({e115}) and 7x user level damage to all enemies.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>89</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Apocrypha</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2-5</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Game table: 2~5 Hits</t>
+          <t>Waste one enemy and lower its phys. DEF ({e162}) with a rare gun.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>94</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Anastasia</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0-4</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Game table: 0~4 Hits</t>
+          <t>Summon the goddess of life to resurrect all allies (HP {e105}).</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>95</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lots Of Guns</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1-5</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Game table: 1~5 Hits</t>
+          <t>Three firearms in hand, rain lead on random enemies ({e93} hits).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>96</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mesmerize</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>Cancel enemy chants, dances, songs and dolls by outperforming them.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3-5</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Game table: 3~5 Hits</t>
+          <t>Shortened for the battle bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Magical Assault</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Slice a random enemy 2-5 times with friendship power. And swords.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Shortened for the battle bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Elixir</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A secret potion: full HP for the party, debuffs and ailments removed.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Shortened for the battle bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Gimme Gold</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gain 4x the enemies' gold value at the end of battle. (Min. 100)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Shortened for the battle bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jackpot</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deal 77x the user's level in damage to one enemy. Jokers are wild!</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Shortened for the battle bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Todokanai Koi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Damage and likely petrify all enemies by tugging their heartstrings.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Shortened for the battle bar</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2917,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2851,381 +2933,567 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sentence</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Catastrophe</t>
+          <t>Arcane Shield</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inflict a powerful physical attack on one enemy. Inflicts slow ({e122}).</t>
+          <t>Activation rate: about 15% (player guide; the game data holds no figure)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dt22-wiki pages/42.html (Siena): "activation rate is about 15%", measured at Lv1. The entry stores only the reflected share</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Effect_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Bounds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>360</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Full of Guts</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Max HP increased (up to +100).</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+100</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Genocide Rain</t>
-        </is>
+      <c r="A3" t="n">
+        <v>361</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rain arrows down upon all enemies across {e147} turns.</t>
+          <t>Vigor Trio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wiki: 2 volleys, each attacks every enemy twice a turn for 4 turns</t>
+          <t>ATK increased (up to +32).</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+32</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Divine Punishment!</t>
-        </is>
+      <c r="A4" t="n">
+        <v>362</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deal physical damage to an enemy row. {e119} chance of instakill.</t>
+          <t>Kindred Spirits</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Up to max TP +50 and fire resistance +20%.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+50, +20%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nightmare Fall</t>
-        </is>
+      <c r="A5" t="n">
+        <v>363</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to all enemies. {e116} chance of causing sleep.</t>
+          <t>Veteran Soldiers</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Slash resistance increased (up to +25%).</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+25%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Powered-Up Beatdown!</t>
-        </is>
+      <c r="A6" t="n">
+        <v>364</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inflict one enemy with {e96} bash attacks. {e118} chance of stun.</t>
+          <t>Attentive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>INT increased (up to +20).</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Psychowave</t>
-        </is>
+      <c r="A7" t="n">
+        <v>365</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage and lower DEF and magic defense ({e162}) for all enemies.</t>
+          <t>Libra Guard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The original names DEF only; the data also lowers magic defense (163), as the Japanese text says</t>
+          <t>DEF increased (up to +25).</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Avatara</t>
-        </is>
+      <c r="A8" t="n">
+        <v>366</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deal physical damage and {e95} defense-piercing attacks on one enemy.</t>
+          <t>Vagabonds</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AGI increased (up to +20).</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Gjallarhorn</t>
-        </is>
+      <c r="A9" t="n">
+        <v>367</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Activate Circle Brave ({e161}), Circle Protect ({e162}) and Moon Curtain ({e169}) at once.</t>
+          <t>Beyond Human</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shortened ("all at the same time") to make room</t>
+          <t>Stab resistance increased (up to +20%).</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Suppression Arrow</t>
-        </is>
+      <c r="A10" t="n">
+        <v>368</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deal damage with an {e117} chance to silence/freeze. Pierces to the back row.</t>
+          <t>NegaPosi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Max HP and TP increased (up to +50 each).</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+50, +50</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Rapid Storm</t>
-        </is>
+      <c r="A11" t="n">
+        <v>369</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Form up to increase speed ({e168}) and physical accuracy ({e166}) for all allies.</t>
+          <t>Dark and Light</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RES increased (up to +20).</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Evolution</t>
-        </is>
+      <c r="A12" t="n">
+        <v>370</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Increase magic attack ({e173}) and critical rate ({e174}) for all allies.</t>
+          <t>Natural Klutzes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bash resistance increased (up to +20%).</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Bunker Buster</t>
-        </is>
+      <c r="A13" t="n">
+        <v>371</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deal damage and reduce physical attack/defense ({e161}). Pierces to the back row.</t>
+          <t>Eccentrics</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DEX increased (up to +32).</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>+32</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Paralyzing Wind</t>
-        </is>
+      <c r="A14" t="n">
+        <v>372</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inflict a wind attack against all enemies. {e115} chance of paralysis.</t>
+          <t>Flawless Poise</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Up to water and earth resistance +20% each.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>+20%, +20%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Daruma-Drop!</t>
-        </is>
+      <c r="A15" t="n">
+        <v>373</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deal physical damage, with a {e54} chance to delay the target's next turn.</t>
+          <t>Celebrities</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>The wiki gives no figure</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Testament</t>
-        </is>
+      <c r="A16" t="n">
+        <v>374</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deal physical damage and use Shadow Sew ({e123}) against an enemy row.</t>
+          <t>Sales Experience</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Up to wind resistance +20% and AGI +10.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>+20%, +10</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Brain Burst</t>
-        </is>
+      <c r="A17" t="n">
+        <v>375</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deal physical damage to one enemy. {e113} chance of poison/paralysis/sleep.</t>
+          <t>Royal Squadron</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Up to bash resistance +10%, earth +20%.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>+10%, +20%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Happy Banquet</t>
-        </is>
+      <c r="A18" t="n">
+        <v>376</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Increase Pep ({e66}) for the ally whose Pep is the lowest.</t>
+          <t>Graceful Agers</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Up to lightning resistance +20% and max HP +50.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>+20%, +50</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Hysteric Slap</t>
-        </is>
+      <c r="A19" t="n">
+        <v>377</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inflict {e94} bash attacks on an enemy row.</t>
+          <t>Mission Ongoing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Up to fire resistance +10% and ATK +20.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>+10%, +20</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fire of Purgatory</t>
-        </is>
+      <c r="A20" t="n">
+        <v>415</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Attack one enemy ({e88} damage to Undead, Demons, and Apparitions).</t>
+          <t>Board Members</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Same effect and value as God Punch, which says "2x damage"</t>
+          <t>DEX and AGI increased (up to +20 each).</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>+20, +20</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Curse Bullet</t>
-        </is>
+      <c r="A21" t="n">
+        <v>405</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Waste one enemy and poison the target ({e113}) with a rare gun-type weapon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Beast Blitz</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Rough up ({e93} hits) and poison ({e113}) one enemy with the power of darkness.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Durchbruch</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fire two arrows of light that pierce to the back row and may silence ({e117}).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Maid Beam</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>The deadly Maid Beam pierces to the back row and begins petrifying targets ({e120}).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Feuerkraft</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Immolate all enemies and absorb their HP and TP (damage cap {e296}).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Gold Power</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Hurl {e433} of your wallet at one enemy for up to {e296} damage. (You won't get it back.)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>777 Fever</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Dish out paralysis ({e115}) and 7 times the user's level in damage to all enemies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Apocrypha</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Waste one enemy and lower target's phys. DEF ({e162}) with a rare gun-type weapon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Anastasia</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Summon the goddess of life to resurrect all allies (HP {e105}).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Lots Of Guns</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>With three firearms in your hands, rain lead upon your enemies at random ({e93} hits).</t>
+          <t>The New Magi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Up to max TP +50 and fire resistance +20%.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>+50, +20%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>dt22-wiki page 72</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3343,17 +3611,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>party_skill_note</t>
+          <t>line1_values</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(Up to {bounds} at {awards} awards)</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Added after the effect line of a party skill. {bounds} are the bounds of PartySkillBounds joined by " and "</t>
+          <t>yes: line 1 of a skill that deals no damage repeats its values ("(TP transfer bonus 100-140%)"). no: line 1 stays as the game wrote it, the box below has every value. The user chose no on 2026-10-04: it is bloat</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>battle_line_width</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Characters the battle bar draws well (measured by the user on Self-Sacrifice, 2026-10-04). Line 1 of techniques and spells, joint skills and items must fit; a longer sentence is rewritten</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>party_line_width</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Characters the box of the party skill list holds on its effect line (seen on screen: a line of 53 runs over the frame). The award count is drawn on the same screen</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3576,6 +3874,66 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>Fire a single shot certain to hit one enemy for {w} damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Multiple hits on an enemy, crit rate rising.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Multiple {w} hits on an enemy, crit rate rising.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A single shot certain to hit one enemy.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A single {w} shot certain to hit one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A barrage of arrows rains upon all enemies.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A barrage of arrows rains {w} damage upon all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1-3 hits on an enemy, mid-range.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1-3 {w} hits on an enemy, mid-range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Short-range: damage to an enemy.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Short-range: {w} damage to an enemy.</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4427,7 +4785,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Short-range skill. Mid-range water damage to one enemy. May freeze.</t>
+          <t>Short-range skill. Mid-range water damage. May freeze.</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4797,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Short-range skill. Lightning damage to an enemy row. May paralyze.</t>
+          <t>Short-range. Lightning damage to a row. May paralyze.</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4809,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storm of roses: non-elemental damage to all enemies. May poison.</t>
+          <t>Rose storm: non-elemental damage to all. May poison.</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4821,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Short-range skill. Pierce to the back row with stab damage. May slow.</t>
+          <t>Short-range. Stab damage through to back row. May slow.</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4833,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Axe skill. Attack an enemy, then the next one in the turn order.</t>
+          <t>Axe skill. Attack an enemy, then the next in turn order.</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4845,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bow/gun skill. Attack one enemy multiple times with rising crit rate.</t>
+          <t>Bow/gun skill. Multiple hits on an enemy, crit rate rising.</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4857,451 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Whip skill. Attack one enemy 1-3 times, mid-range. Crits on Beasts.</t>
+          <t>Whip skill. 1-3 hits on an enemy, mid-range. Crits on Beasts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Backward Swing</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Katana skill. Bash damage to an enemy. May paralyze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Halving Slice</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Katana skill. Slash damage to a row. May instakill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Armor Penetration</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Katana skill. Defense-piercing damage and DEF down to one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Moonlight Purgatory</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Katana skill. Slash damage 3 times to a living enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Geo Break</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Axe skill. Earth damage to an enemy. May petrify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cross Slash</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sword/lance skill. Attack an enemy (strong vs. unholy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gust Thrust</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lance skill. Wind damage to an enemy. May silence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Daedalus Attack</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lance skill. 3-5 hits on random enemies. Heavy Lance bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pursuit Stab</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dagger skill. Stab damage based on enemy buffs and debuffs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sleep Sting</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Short-range: damage to an enemy. May cause sleep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Silence Sting</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Short-range: damage to an enemy. May silence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Stun Sting</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Short-range: damage to an enemy. May stun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Guided Shot</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bow/gun skill. A single shot certain to hit one enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Spiral Arrow</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bow skill. Shoot a powerful single shot at an enemy for stab damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Freeze Shot</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bow skill. Stab damage to an enemy. May freeze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Paralysis Shot</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bow skill. Stab damage to an enemy. May paralyze.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Arrow Rain</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bow skill. A barrage of arrows rains upon all enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Divine Cannon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bow skill. Stab damage to an enemy, piercing to the back row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Projectile skill. Attack and lower speed for an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Bible Thump</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tome skill. RES-based bash damage. May freeze/silence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Treasure Search</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Detect how many unopened treasure chests are left on this floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Debilitating Salsa</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dance skill. Damage all enemies at the start of each of your turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Emaciating Hopak</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Dance skill. Lower all enemies' elemental resistances while dancing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Surprise Fist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>50/50: non-elemental damage to each enemy. May stun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tinker Squash</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fan skill. Bashing damage. May delay enemy turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Graceful Rose</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fan skill. With raised ATK, deal long-range damage to an enemy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Life Bringer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Short-range. Attack an enemy and reduce its max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Shine Curse</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Non-elemental damage to all enemies (strong vs. unholy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Moon Curtain</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Raise party resistance to fire, water, lightning, wind, and earth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Fire Scroll</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fire damage by enemy max HP and lower ATK to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Water Scroll</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Water damage by enemy max HP and lower magic def. to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Lightning Scroll</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lightning damage by enemy max HP and lower speed to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Wind Scroll</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Wind damage by enemy max HP and lower evasion to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Earth Scroll</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Earth damage by enemy max HP and lower DEF to an enemy row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Primevil</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sacrifice yourself to revive, heal, and cure the rest of the party.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Prism Dawn</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hit both rows with a raw magic attack plus RES-based damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Soul Eater</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deal enormous damage to a living enemy. Low chance of instakill.</t>
         </is>
       </c>
     </row>
@@ -4514,7 +5316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4538,6 +5340,11 @@
           <t>Labels</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Figures</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4555,6 +5362,11 @@
           <t>Critical rate | Enemy critical rate</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4572,6 +5384,11 @@
           <t>Physical evasion | Magic evasion</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4589,6 +5406,11 @@
           <t>Magic damage | Magic accuracy</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4606,6 +5428,11 @@
           <t>Max HP damage</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4623,6 +5450,11 @@
           <t>Max HP damage | ATK</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4640,6 +5472,11 @@
           <t>Max HP damage | Magic defense</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4657,6 +5494,11 @@
           <t>Max HP damage | Speed decrease</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4674,6 +5516,11 @@
           <t>Max HP damage | Evasion</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4691,6 +5538,11 @@
           <t>Max HP damage | DEF</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4708,6 +5560,11 @@
           <t>HP on revival</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4725,6 +5582,11 @@
           <t>DEF | Magic defense</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4742,6 +5604,11 @@
           <t>Post-battle HP | Post-battle TP</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4759,6 +5626,11 @@
           <t>Conversion success</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4776,6 +5648,11 @@
           <t>Shadow Sew Success</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4793,6 +5670,11 @@
           <t>Activation rate</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4802,12 +5684,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Whip skill. Deal {dmg} bash damage twice. May silence ({0})/paralyze ({1}).</t>
+          <t>Whip: {dmg} bash damage twice. Silence ({0}), paralyze ({1}).</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>Silence | Paralysis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>chances</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Item sentences shortened by hand so that sentence + (data) fits one line of 85 characters.</t>
+          <t>Item sentences shortened by hand so that sentence + (data) fits the battle bar (Settings/battle_line_width).</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yakisoba noodle bread. Sells out very quickly.</t>
+          <t>Yakisoba noodle bread. Sells out fast.</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Premium steak sandwich, luxury sauce. Extra deluxe.</t>
+          <t>Steak sandwich, luxury sauce. Deluxe.</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spicy curry that would make even a Maharaja groan.</t>
+          <t>Curry to make a Maharaja groan.</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Legendary food. Whoever eats it falls in love.</t>
+          <t>Legendary. Eat it and fall in love.</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Highly nutritious, it heals HP and TP but is extremely bitter.</t>
+          <t>Nutritious, heals HP and TP, but extremely bitter.</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Beard's special bento. Balanced, big enough to share.</t>
+          <t>Beard's special bento, made to share.</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kumaya Mangetsudo's anpan. Low-calorie, but still delicious.</t>
+          <t>Kumaya Mangetsudo's low-calorie, tasty anpan.</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mary Florina's rich milk collagen gel.</t>
+          <t>Mary Florina's milk collagen gel.</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A cure for anything, and plenty of it.</t>
+          <t>A cure for anything, and plenty.</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rock-hard cracker. Snack and emergency ration!</t>
+          <t>Rock-hard snack and emergency food!</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wind that brought spring to the underworld.</t>
+          <t>Spring wind of the underworld.</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Whatever's under the breading, it's good and fried.</t>
+          <t>Whatever's in the breading, it's good fried.</t>
         </is>
       </c>
     </row>
@@ -4119,7 +4119,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vial of mysterious holy water. Tiny waves ripple at the top.</t>
+          <t>Mysterious holy water. Tiny waves ripple on top.</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>If this waits back at base, someone's about to die.</t>
+          <t>If it waits at base, someone's about to die.</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A skull from a secret rite. Grants wishes.</t>
+          <t>Rite skull. Grants wishes.</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A branch only some may pray to. It's twig-sclusive.</t>
+          <t>A branch only some may pray to. Twig-sclusive.</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>It might take... one more hit. Hit it baby one more time.</t>
+          <t>One more hit... Hit it baby one more time.</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Do the goggles switch her personality, or just add confidence...?</t>
+          <t>Do they switch her personality, or add confidence...?</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>It'll send you to another world with just one sip (it's poison).</t>
+          <t>One sip sends you to another world (it's poison).</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A chain worn down by too much grinding. Kinda like my ex.</t>
+          <t>Worn down by too much grinding. Kinda like my ex.</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Collect seven of these to summon a wish-granting dragon.</t>
+          <t>Collect seven to summon a wish-granting dragon.</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Press it for peace at any cost. There may be consequences...</t>
+          <t>Peace at any cost. There may be consequences...</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sweet persimmons preserved with sulfur. Tasty.</t>
+          <t>Sweet sulfur-preserved persimmons. Tasty.</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sushi in persimmon leaves. Don't eat the leaves.</t>
+          <t>Don't eat the persimmon leaves.</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bear-meat citatap stew with pukusakina and veggies.</t>
+          <t>Bear citatap stew with pukusakina.</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hot fried chicken. Ask before you add lemon juice.</t>
+          <t>Hot fried chicken. Ask before the lemon.</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Feel refreshed by the mint's cold, transcendent stimulation.</t>
+          <t>Cold, transcendent minty stimulation.</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Three aspects of the dumpling on one skewer.</t>
+          <t>Dumpling trinity on one skewer.</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Raw meat cut fine and called a steak. Eat with caution.</t>
+          <t>Raw meat called a steak. Eat with caution.</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Syrup and dry fruit. A hard candy for hard men.</t>
+          <t>A hard candy for hard men.</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cake with a figurine. Whoever finds it gets to be king.</t>
+          <t>Find the figurine, be the king.</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Off the shelf or classy? Really not that different.</t>
+          <t>Shelf or classy? Not that different.</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Party pastry of fruits, custard, and jelly.</t>
+          <t>Fruit, custard, jelly. Party!</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A cookie in a complex shape. Looks like Japan!</t>
+          <t>Cookie that looks like Japan!</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rare, top-notch candy from the demon world.</t>
+          <t>Top candy of the demon world.</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Served without a warning, you're the butt of a joke.</t>
+          <t>Served unwarned, you're the butt of a joke.</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A flattened octopus. Plenty to go around.</t>
+          <t>Flat octopus. Plenty for all.</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Red bean bun of fine gold wheat. Diabetics should avoid it.</t>
+          <t>Fine gold wheat bun. Diabetics, avoid it.</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>So spicy it's out of this world. One call and they deliver.</t>
+          <t>Out-of-this-world spicy. They deliver.</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sticky pudding with raisins. Just pudding. Honestly.</t>
+          <t>Just raisin pudding. Honestly.</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Soup made of leftovers. Liver and let die!</t>
+          <t>Leftovers. Liver and let die!</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The unagi's not always good, but the sauce is.</t>
+          <t>Come for the sauce, not the eel.</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dead eels on rice. You wouldn't want any.</t>
+          <t>Dead eels on rice. You'd pass.</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sushi roll of sticky, smelly, fermented soybeans. Yum...?</t>
+          <t>Sticky, smelly soybean sushi. Yum...?</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bitter jelly good for the skin. Not so great for the tortoise.</t>
+          <t>Good for the skin. Not so for the tortoise.</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Genuine, real turtle soup! Would I lie to you?</t>
+          <t>Real turtle! Would I lie to you?</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Made in an earthenware pot. Delicious but steep.</t>
+          <t>Earthenware pot. Delicious but steep.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cheap and delicious. Sometimes filled with pudding.</t>
+          <t>Cheap, tasty. Sometimes has pudding.</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Handle it with care, or the cream will spurt all over you.</t>
+          <t>Careful, or the cream will spurt all over you.</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Triple-stack of pancakes in sticky maple syrup.</t>
+          <t>Triple-stack in maple syrup.</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>A luxury item perfect for souvenirs or gifts.</t>
+          <t>A luxury souvenir or gift.</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Its mascot creature has yet to be identified by science.</t>
+          <t>Its mascot is still unidentified by science.</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bavarian cream full of slime. Appetizing?</t>
+          <t>Full of slime. Appetizing?</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Feeling foreign. You're a stranger in a strange land.</t>
+          <t>You're a stranger in a strange land.</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Canned dragon meat. Rare, expensive, a little smelly.</t>
+          <t>Rare, pricey, slightly smelly meat.</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Some never tried this sake, but none tried it only once.</t>
+          <t>Some never tried it, none tried it only once.</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sake that intoxicates even heavy drinkers. Super harsh.</t>
+          <t>Intoxicates even heavy drinkers. Super harsh.</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Meat that shines suspiciously. Steroids in meat form.</t>
+          <t>Shines suspiciously. Steroids as meat.</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Unrelated to the anime girl whose face gets eaten.</t>
+          <t>Not the anime girl whose face gets eaten.</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A mandra trefoil, used as a graduation charm.</t>
+          <t>A mandra graduation charm.</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fresh-squeezed mandra juice. Nice and pulpy.</t>
+          <t>Fresh-squeezed and pulpy.</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Made to achieve sake supremacy. To sake-cceed.</t>
+          <t>For sake supremacy. To sake-cceed.</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Denizens of the world above say these pair well with tea.</t>
+          <t>Heaven's denizens pair these with tea.</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sweet-smelling beverage of liquified mana crystals.</t>
+          <t>Sweet drink of liquified mana crystals.</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,1639 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Drink that lights a fire in your loins. Yowch! Hot!</t>
+          <t>Lights a fire in your loins. Yowch! Hot!</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Mui Kuha Medicine</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Revive a fallen ally. Very bitter aftertaste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Kuding Tea</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Condensed bitterness. An acquired taste, I hear...</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Super Rich Pudding</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Peggy's eggy milk pudding. Said to be legendary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Peggy's Revivifying Tonic</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A new way to cheat death, by the Peggy Company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Prayer Icon</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>An aged icon that's heard years of prayers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Round of Revolution</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>A shell left by one who died for the revolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Golden Iron Chunk</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>A well-made futuristic metal. A bit lumpy. Weird.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Dark Power</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>It scrambles your brain, then you die. No coming back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Rune Amulet</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Wish-granting runes. Impressive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Devil-Sealing Pot</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>I peeked in, it peeked back... Someone's in there!</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Deer Boy's Antlers</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Maybe usable in traditional medicine... maybe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Indulgence</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Might's not all that makes right. Money does too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Bad Report Card</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>I must leave on a long, long journey. Don't look for me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Red Feather</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>A red feather you get for donating to a cause.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Spider Web</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>The rain came down, but this web stayed put.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Deathly Poison Needle</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>One prick would be disastrous. Handle with care.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Johari Mirror</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>A mirror that shows the truth... You may not want to look.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Soil of Life</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Clay of the heavens. Heh. They soil themselves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Napolitan Spaghetti</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pan-fried. A steal at 3 million lira!</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Breezy Timbre</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>No wind blows, yet you hear its sound. It cries Mary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Refreshing Eye Drop</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>One drop refreshes constantly overworked eyes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Eternal Flame</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Blowing or water won't put it out. We didn't start it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>The fruit, sadly, not the event. Sweet, packed with energy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Pineapple Cake</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>A pastry for the prosperous. Crumbly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senmei Root</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Makes a nice crunch when you bite into it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Geta With a Cut Strap</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Useless sandals. Might as well toss 'em.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cleaver Sharpener</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ruined your good cleaver on bone? Finally, there's help!</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mermaid Meat</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Eat it and die on the spot... or never.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ancient Awamori</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Rice liquor aged for more than three years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Toad Oil</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Oil for wounds instead of salve. If you want.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Forced Comforter</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>You were forced to buy it at 5x the price. I could cry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Lucky Chain Letter</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>It says it's lucky. Can't believe all you read, can you?</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Youthful Love Letter</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>It simply says: You are my fire. My one desire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Graduation Yearbook</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Prompt: who's your personal hero? I wrote, 'Me.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Tiger Scroll</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tiger scroll of the innermost secrets of martial arts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ganges Water</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Holy river water full of extracts. Extracts...</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Natural Oils</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>For massages, hair care, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Paper Crane of Prayers</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>An origami crane with a great many folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Trap Box</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Shoots out needles when opened improperly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Box of Contracts</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Contracts signed under threat of violence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Stinky-Gripped Sword</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>A sword with a bamboo grip. Somehow the grip... reeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Headless Doll</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>It has no head, yet you swear you've heard it giggle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Lifelike Doll</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Press its nose and it changes to look just like you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Spooky Photo</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Each time you look, the people are in different poses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Portable Grill</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Not for indoors. DEFINITELY not for use in a vehicle!</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Long Nail</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>For voodoo curses. Picture your enemy, give it your all!</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Fuligin Thunder</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Crackin' chocolate. Ladies love it!</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Apple of Discord</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Tempts women into strife.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Bonsho Bell</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Huge bell that wards off evil. Awkward to carry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Evergreen Wellwater</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Water from a shrine to a god of the land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Dragon Tonic</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Fruit in the dragon, this out. Don't ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Dragon Pacifier</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Tough enough for a mouth full of dragon baby teeth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Eternal Darkness</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Strange substance. Touching it feels like nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Snooze Box</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Not for napping in. For hiding nappers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Golden Mask</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Just gold in color. Not all that glitters is gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Palytoxin</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Dangerous! Do not touch! Deadly poison!</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Tetanus Toxin</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Dangerous! Do not touch! Deadly poison! #2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Ferryman's Boat</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Nice rowboat. Cruise the river between life and death.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Underworld Tea</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sweet mint immortali-tea. Beyond relaxing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Lump of Jealousy</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Jealousy so thick you can see it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>One-Eyed Fish</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Stay away from the water this came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Ghost Extract</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Toss it in any potluck stew for instant chaos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Scrabbling Hand</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Disembodied wrist. Scurries about like a cleaning robot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Longevity Peach</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Peach-shaped bun for celebrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Hong Shao</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Slightly disgusting simmered bear paw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Kofta</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Fried lamb meatballs. Smells of coriander.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Bird Bear Lunch Set</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Bird meat and bear meat, mixed together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Penguin Oil</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Brave penguins died to bring you fuel and soap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Rainbow Drug</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sketchy in seven ways. Get it? Seven rainbow colors!</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Chestnut Rice</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Steamed rice with big pieces of chestnut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Madeleine</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Sally sells these seashells by the shore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Muffin</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Not all who eat muffins are mafia. The muffia? Hyuk hyuk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Simple Cookie</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>A simple-shaped cookie. Ooh, looks like a star!</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Middling Cookie</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>A somewhat complex cookie. Ooh, looks like a cow!</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Super Spicy Cracker</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Rice cracker covered in cayenne powder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Saucy Cracker</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Just a cracker with sauce, but dang, tasty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Kneaded Candy</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Colorful candy kneaded with two sticks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Fortune Candy</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Long candy, long life. It's just math.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Hamburg with Egg</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Egg on a patty. When to break the yolk...?</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Festive Monaka</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Sesame, white bean and... red bean paste!</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Colorful Macarons</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Bright macarons in assorted colors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Muscle Protein</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Planet Muscle staple. From ripped to jacked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Soy-glazed Kombu</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>You should stop but can't kelp yourself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Soy-glazed Waterbug</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Bad looks, worse texture, weirdly addictive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Huge Takoyaki</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>The main sustenance of one particular race.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Baklava</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Nothing but sweet. Not to be confused with balaclava.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Choco Fudge</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>A runny, sugary snack. Calories through the roof.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Moffle</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Rice flour waffle. Comes out mochi-ish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Stroopwafel</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Sweet waffle with syrup in the batter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Royal Pancake</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Overpriced-hotel luxury pancakes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Choco Cornet</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Which end to eat first? A matter of scholarly debate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Black Bread</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Tough rye bread. A challenge for weak teeth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Rap Candy</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Brings the urge to rap. You'll be a real Kandy-e West.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Crispy Rusk</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>High-class white chocolate rusk. Mindblowingly delicious.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Super Pixie Stick</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Candy so sweet your brain will melt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Mouthmelter Ramen</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>You'll sweat from every orifice you've got.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Jolokia Curry</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>First-timers pass out from the spice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Bean-Filled Donut</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Donut with red bean paste inside, sugar coating outside.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Matcha Taiyaki</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Matcha in the batter. Looks a little gross.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Chocolate Mushroom</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Hill shrooms despise the coddled city bamboo shoots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Mattake</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Formerly known as matsutake. They're... fine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Susshroom</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Yellow with red spots. Eat it and you may grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Imperial Sucai</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Opulent vegetable dish. No meat. For some reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Imagawa-yaki</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Cakey treat filled with red bean paste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Bean Paste Cake</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Ol' reliable. Bean paste can't go wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Kusaya-Don</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Mind your surroundings when eating this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Seaman Sashimi</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Grotesque when the fish has a man's face.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Honkarebushi</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Bonito so dry it's a blunt weapon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Kanpyo-Maki</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Simple but deep. Order it last to look cultured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Yakiniku Bento</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Only meat and rice. Veggies, get out of here!</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Special Sukiyaki Bento</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Sukiyaki bento with super luxurious wagyu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Yellow Soda</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Call it yellow and a rep will appear to call it gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Moonshine Bomb</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Go easy if you like your brain cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Herb Mochi</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>You can never have too much mugwort!</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Mont Blanc</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>White mountain, yellow cake. Y u do dis?</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Mille-Feuille</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Multi-layered doughy pie cake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Momiji Manju</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Maple leaf souvenir. Even better as ice cream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Raksi</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Millet liquor. Its mature flavor can be a habit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Yamatoni</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Canned whale. Vanishing from shelves.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Slime Bar</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Only the gloopiest cuts of slime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Nastiness in a Can</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Spray that makes you a super sadist for a few minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>100 Year Port</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Port wine aged for over a hundred years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Dragon Kiviak</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Waterfowl shoved into a dragon corpse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Thunderbringer</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>So hard, a bite might chip your tooth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Nearly Rotten Meat</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Meat is best when almost rotten... or so they say.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1000% Apple Juice</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Squeezed from an apple creature's guts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1000% Melon Juice</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Squeezed from a melon creature's guts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1000% Banana Juice</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Squeezed from a banana creature's guts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Mandra Root</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Herbal medicine with a strong scent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Dried Mandra</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Too much causes hallucinations. Not the good kind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Four-Leaf Mandra</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Said to bring luck. Does anyone believe that?</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Sun Cake</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Rice cake that crumbles as you eat it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Sea Palace Orb</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>The Dragon Palace's most treasured treasure...</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Green bud held by the former ruler of the world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>New World Egg</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>There's a whole new world inside it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Euthys's Medal</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Proof you attended all of Miss Euthys's lectures.</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JointSkillSentences" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueSkillNotes" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PartySkillBounds" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OutOfGameWords" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -652,7 +653,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unique skills: a line added under the box for a figure that only a guide gives (it says so).</t>
+          <t>Unique skills: a line added under the box for a figure the entry does not store. In the voice of the game; its origin goes in the Source column, never in the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OutOfGameWords</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hard rule of the user: no text shown in the game may break the game's voice. A text the mod writes that contains one of these words (as a whole word, any case) stops the build. Where a figure comes from is recorded in these sheets, never on screen.</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2963,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Activation rate: about 15% (player guide; the game data holds no figure)</t>
+          <t>Activation rate: about 15%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3502,6 +3515,264 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Word</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>guide</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>wiki</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>game data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>the data</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>binary</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>decoded</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>not known</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>player test</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>the game</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mod</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>vanilla</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>original text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>unconfirmed</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>not confirmed</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tbd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>todo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Speaks from outside the game</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -25,6 +25,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueSkillNotes" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PartySkillBounds" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OutOfGameWords" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueSkillLabels" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -666,6 +667,18 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>Hard rule of the user: no text shown in the game may break the game's voice. A text the mod writes that contains one of these words (as a whole word, any case) stops the build. Where a figure comes from is recorded in these sheets, never on screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UniqueSkillLabels</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Unique skills: what the numbers of the box measure, written in place of "Lv1-9". A skill without a row keeps "Lv1-9" (what its number measures is not known).</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2976,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Activation rate: about 15%</t>
+          <t>Activation rate: 15%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3773,6 +3786,263 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Third Eye Wide</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sugar Coma</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Furious Strike</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Alter Fate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Usurper of Souls</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Overstock Clearance</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Did You Call for Me?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tranquil Song</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Forerunner</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The sentence says it happens sometimes ("may", "occasionally") and the entry stores one rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Elbow Grease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Weapon modifier</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>"Increase weapon modifier": the stored value is that increase</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Wreathed in Glory</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Turn delay</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>"Decrease turn delay": the stored value is that decrease</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Maximum Maid</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Maid skill effects</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>"Increased effects for all maid skills"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Arcane Shield</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Reflected</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/42.html: the stored value is the share reflected (50% at Lv1, 200% with the crown)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -26,6 +26,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PartySkillBounds" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OutOfGameWords" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueSkillLabels" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFixes" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -679,6 +680,18 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>Unique skills: what the numbers of the box measure, written in place of "Lv1-9". A skill without a row keeps "Lv1-9" (what its number measures is not known).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ScriptFixes</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lessons, tutorials and shop dialogue: a sentence that states a rule wrongly, and its correction. The replacement must have exactly as many bytes as the original (pad with a trailing space): scripts are bytecode and are never resized.</t>
         </is>
       </c>
     </row>
@@ -4201,6 +4214,85 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Original</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Teaching.pck</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CheatsTeaching_25.adv.bin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>When level resetting, if there is a gap of over 59 between
+your former level and the level you're resetting to,
+all your stats will increase by 1.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When level resetting, if the gap is 59 or greater between
+your former level and the level you're resetting to,
+all your stats will increase by 1. </t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>The tutorial says "over 59"; the lesson (BattleTeacher_Sp03) says "59 or greater" and so does the DT2-2 wiki (pages/79.html: a drop of 59 to 68 levels gives +1). One trailing space keeps the length.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -818,6 +818,11 @@
           <t>Harmful</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1483,6 +1488,336 @@
       <c r="F45" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>27</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>{v}% speed up</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>100</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: chance of action speed up (Starfall Bracelet, Accelerator, Highway Pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fire Blast Lv{v}</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ice Storm Lv{v}</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Thunder Chain Lv{v}</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Air Turbulence Lv{v}</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>51</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Soul Absorb Lv{v}</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>93</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ice Edge Lv{v}</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>98</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Muon Plasma Lv{v}</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>101</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tempest Lv{v}</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>102</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Stone Hammer Lv{v}</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>103</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Meteor Lv{v}</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>104</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gaia Crush Lv{v}</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>106</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Rainbow Flash Lv{v}</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the item casts this spell; the stored value is its level (6 of the 8 levels the wiki gives equal the enemy-side value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>69</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>party cures freeze</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: Whale Soup also cures freeze</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>88</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>enemies flee</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>DT2-2 wiki pages/36.html: the enemy runs away (Cloaking Device)</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B202"/>
+  <dimension ref="A1:B222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7009,6 +7344,246 @@
       <c r="B202" t="inlineStr">
         <is>
           <t>Proof you attended all of Miss Euthys's lectures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Book of the Fist</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Every style of a master fistfighter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Lolita Stick</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>A kids' toy stick. Get your mind out of the gutter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Void Thunder</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>A glass bottle of pure electricity. Shocking!</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Deathly Black Torch</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Creepy black fire, burning since the world's turning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Soul Pact</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>No contracts with your soul. Even with other humans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Rainbow Gem</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>A self-powered gem. Apparently created by fairies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Melange</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Spice that flows smoothly. Good, because it must.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Glacier Fragment</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Ice all too available in the distant northern seas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Turtle Cake</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Auspicious red and white. Only turtle-shaped!</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Magic Globe</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Spin it and feel as if you rule the world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Crystal Skull</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>A clear, shining crystal. It's missing one eye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Rainbow Fluid</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>The seven-colored liquid rainbows are made of.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Lost Continent Soil</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Lost continent soil. Rich in potassium and mystery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Habaki Figurine</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Ancient doll so weird, it's gotta be extraterrestrial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Rain Incense</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Burned to pray for rain. Works great... as prayers go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Bloody Menorah</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Menorah smothered in blood. Definitely not kosher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Perpetual License</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Why let it expire when you die? Licensed forever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Accelerator</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Raise your clock rate for a while.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Cider</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>The carbonation feels good sliding down your throat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Whale Soup</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Toss whale in soup. Get this.</t>
         </is>
       </c>
     </row>
@@ -7974,7 +8549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8996,6 +9571,27 @@
         </is>
       </c>
       <c r="E48" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>extra</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>170</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Enmity</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>num</t>
         </is>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -2580,12 +2580,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>signed_points_pct</t>
+          <t>signed_num</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>All resistances, in points (one point is 1%)</t>
+          <t>All resistances, in points, written as the status screen writes them (+25)</t>
         </is>
       </c>
     </row>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Up to max TP +50 and fire resistance +20%.</t>
+          <t>Up to max TP +50 and fire resistance +20.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+50, +20%</t>
+          <t>+50, +20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slash resistance increased (up to +25%).</t>
+          <t>Slash resistance increased (up to +25).</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+25%</t>
+          <t>+25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stab resistance increased (up to +20%).</t>
+          <t>Stab resistance increased (up to +20).</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bash resistance increased (up to +20%).</t>
+          <t>Bash resistance increased (up to +20).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Up to water and earth resistance +20% each.</t>
+          <t>Up to water and earth resistance +20 each.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>+20%, +20%</t>
+          <t>+20, +20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Up to wind resistance +20% and AGI +10.</t>
+          <t>Up to wind resistance +20 and AGI +10.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>+20%, +10</t>
+          <t>+20, +10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Up to bash resistance +10%, earth +20%.</t>
+          <t>Up to bash resistance +10, earth +20.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+10%, +20%</t>
+          <t>+10, +20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Up to lightning resistance +20% and max HP +50.</t>
+          <t>Up to lightning resistance +20 and max HP +50.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+20%, +50</t>
+          <t>+20, +50</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Up to fire resistance +10% and ATK +20.</t>
+          <t>Up to fire resistance +10 and ATK +20.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>+10%, +20</t>
+          <t>+10, +20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Up to max TP +50 and fire resistance +20%.</t>
+          <t>Up to max TP +50 and fire resistance +20.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+50, +20%</t>
+          <t>+50, +20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4397,7 +4397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4541,6 +4541,23 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Characters the box of the party skill list holds on its effect line (seen on screen: a line of 53 runs over the frame). The award count is drawn on the same screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>percent_points</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>critical rate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Skill values stored in points that are written with % (regular expression on the game's phrase). Resistance is not here: the game writes it as a plain number (Bs Res -20), and so does the mod</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9599,6 @@
           <t>extra</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>170</v>
       </c>
@@ -10581,7 +10597,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10596,7 +10612,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10611,7 +10627,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10626,7 +10642,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -10641,7 +10657,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -10656,7 +10672,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -10671,7 +10687,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -10686,7 +10702,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -10701,7 +10717,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -10716,7 +10732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10731,7 +10747,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10746,7 +10762,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10761,7 +10777,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10776,7 +10792,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10791,7 +10807,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10806,7 +10822,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10821,7 +10837,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -10836,7 +10852,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -10851,7 +10867,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10866,7 +10882,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10881,7 +10897,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10896,7 +10912,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10911,7 +10927,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10926,7 +10942,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10941,7 +10957,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>+15%</t>
+          <t>+15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10961,7 +10977,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10981,7 +10997,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>-15%</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11001,7 +11017,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11021,7 +11037,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>+75%</t>
+          <t>+75</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11041,7 +11057,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>-30%</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11061,7 +11077,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11081,7 +11097,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11101,7 +11117,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>+25%</t>
+          <t>+25</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11121,7 +11137,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11141,7 +11157,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>-20%</t>
+          <t>-20</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11161,7 +11177,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11181,7 +11197,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11196,7 +11212,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11211,7 +11227,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11226,7 +11242,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11241,7 +11257,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11256,7 +11272,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11271,7 +11287,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11286,7 +11302,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>+50%</t>
+          <t>+50</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11301,7 +11317,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11316,7 +11332,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11331,7 +11347,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11346,7 +11362,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -11361,7 +11377,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -11376,7 +11392,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -11391,7 +11407,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -11406,7 +11422,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+100</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -11421,7 +11437,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -11436,7 +11452,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -11451,7 +11467,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11466,7 +11482,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -11481,7 +11497,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -11496,7 +11512,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -11511,7 +11527,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -11526,7 +11542,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>-50%</t>
+          <t>-50</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1818,6 +1818,83 @@
       <c r="G60" t="inlineStr">
         <is>
           <t>DT2-2 wiki pages/36.html: the enemy runs away (Cloaking Device)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>29</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>{v}% Accelerator</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>100</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Read in the program: the class of this effect type performs the skill (tools/item_effect_data.py, docs/FORMULAS.md 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>32</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>{v}% War Cry</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>100</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Read in the program: the class of this effect type performs the skill (tools/item_effect_data.py, docs/FORMULAS.md 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>90</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fireball Lv{v}</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Read in the program: the class of this effect type performs the skill (tools/item_effect_data.py, docs/FORMULAS.md 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>89</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>lose 5% of gold</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Read in the program: a twentieth of the gold held, at least 1; the stored value is not used (0x51438a)</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3406,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dt22-wiki pages/42.html (Siena): "activation rate is about 15%", measured at Lv1. The entry stores only the reflected share</t>
+          <t>Read in the program: a number below 100 under 15 (0x424766, docs/FORMULAS.md 12.19). The DT2-2 wiki measured about 15%</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4383,6 +4460,74 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>DT2-2 wiki pages/42.html: the stored value is the share reflected (50% at Lv1, 200% with the crown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shadow Heart</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 12.19): rolled before her action</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Undaunted Spirit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Activation rate</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 12.19): rolled at the end of each turn while she is fallen</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Yearning</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Class modifiers (%)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 12.19): each point adds 0.01 to every class modifier (10.4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Positive Trance</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pep over 100 per +1% damage</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 12.19) and 2.4: damage gains (Pep - 100) / value percent</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9608,6 +9753,66 @@
         </is>
       </c>
       <c r="E49" t="inlineStr">
+        <is>
+          <t>num</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>extra</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>171</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Cover ends per hit</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>extra</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>180</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Parry ends per block</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>extra</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>147</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Turns on field</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>num</t>
         </is>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1895,6 +1895,116 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>Read in the program: a twentieth of the gold held, at least 1; the stored value is not used (0x51438a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>54</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>{v}% max HP damage up to 100</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>100</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 15): int(max HP * value), never above 100, never the last HP (0x511b56 - 0x511b8e)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>55</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>{v}% max HP damage</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 15): int(max HP * value), never the last HP (0x511e25 - 0x511e52)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>56</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>{v}% max HP damage</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>100</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 15): its case of the switch enters the class of type 55 (0x50d62f)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>60</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>silences Apparitions</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 15): on an enemy of race 7, creates Silence with the stored value (100) for 5 turns (0x512935 - 0x51296e)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>61</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>{v}% HP to Beasts</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>10</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 15): on a unit of race 2, restores max HP * value / 10, with Item Mastery (0x512bd1 - 0x512c9b)</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4528,6 +4638,23 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>Read in the program (docs/FORMULAS.md 12.19) and 2.4: damage gains (Pep - 100) / value percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Demon Wall</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Taken</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 12.19): added to the damage cut against the three races. "Damage taken" is one character too long for the line</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4703,6 +4830,40 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Skill values stored in points that are written with % (regular expression on the game's phrase). Resistance is not here: the game writes it as a plain number (Bs Res -20), and so does the mod</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>enemy_power_label</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Label of the power of a physical enemy attack on its data line (EnemyAttackData 0x3C: what the attack adds to the modifiers of its attack value, docs/FORMULAS.md 9.2), written as a signed percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>enemy_power_scope</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>summons</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Which attacks show it. summons: only the attacks a summon of the player can use (tools/summon_data.py), the screen where these texts were seen. The user chose this on 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B222"/>
+  <dimension ref="A1:B234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7746,6 +7907,150 @@
       <c r="B222" t="inlineStr">
         <is>
           <t>Toss whale in soup. Get this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Beast Chow</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Beasts love it! Flavor and nutrition just right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Firecracker</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>A Souffle special. Bang!</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Ephemerol</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Pregnancy sedative. Side effects...</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Chemical 4869</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Secret organization pill. Do not eat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Fairy Tonic</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Liquor of crushed fairies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Gravestone Shard</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Stone under which sleeps a king of gamblers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Water of Wrath</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Malicious water, stuck in its bottle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Horse Jerkey</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Aged, smoked horse meat. Exquisite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Jellied Ray</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Smells like a filthy public toilet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Surstrsomething</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Mistaken for a chemical weapon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Habanero Cider</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Sweet and spicy... What evil genius made this??</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Spicy Sambal Lassi</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Pointless. Unbearably hot.</t>
         </is>
       </c>
     </row>
@@ -9809,7 +10114,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Turns on field</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -4669,7 +4669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4864,6 +4864,36 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>Which attacks show it. summons: only the attacks a summon of the player can use (tools/summon_data.py), the screen where these texts were seen. The user chose this on 2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>skill_wide_line</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>92</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Characters a line of the skill box may reach once its separators are widened. The content of a line is still chosen for line_width (85); the screenshot of Heal of 2026-10-05 shows a line of 73 characters ending at three quarters of the box</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>skill_separator_pad</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Spaces on each side of the bar between two items of a skill box line, when the widened line stays within skill_wide_line. The user asked for air on 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9319,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HP recovery</t>
+          <t>Heals RES</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>half_mult</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -27,6 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OutOfGameWords" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueSkillLabels" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFixes" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MealBuffs" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -692,6 +693,18 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>Lessons, tutorials and shop dialogue: a sentence that states a rule wrongly, and its correction. The replacement must have exactly as many bytes as the original (pad with a trailing space): scripts are bytecode and are never resized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MealBuffs</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Meals: the words of a meal sentence that name the buff of each effect type. The build writes after them the level the program gives the buff, read from the executable</t>
         </is>
       </c>
     </row>
@@ -4981,6 +4994,269 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fire Enchant</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Water Enchant</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lightning Enchant</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wind Enchant</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Earth Enchant</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Stab, Slash, and Bash Guard</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Divine Shield</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>82</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Accelerator</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>84</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fleet Foot</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>85</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>86</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>The level is written in the program (tools/item_effect_data.py, meal_buffs) and is the one the game announces when the meal is eaten (StringData 183 to 196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brave</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>The program performs the party version of the skill at its last level (0x50b0ea asks the skill table for the number of levels)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>36</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>The program performs the party version of the skill at its last level (0x50b0ea asks the skill table for the number of levels)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>39</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sun Veil</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>The program performs the party version of the skill at its last level (0x50b0ea asks the skill table for the number of levels)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Phrase: the words of the meal sentence that name the buff of this effect type; the build writes "Lv N" after them.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -773,6 +773,23 @@
         </is>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Directly decompiled from DT2-2 unwrapped x86 executable</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -10445,7 +10462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10938,12 +10955,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The DT2-2 wiki lists this one as unknown (-??%)</t>
+          <t>x86: 0x4f83b6 (-10% Max HP)</t>
         </is>
       </c>
     </row>
@@ -10958,12 +10975,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>First game: stacks up to +50%</t>
+          <t>x86: 0x44b69a (mulss 4.0)</t>
         </is>
       </c>
     </row>
@@ -10978,12 +10995,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>First game: stacks up to +50%</t>
+          <t>x86: 0x44df30 (mulss 4.0)</t>
         </is>
       </c>
     </row>
@@ -10998,12 +11015,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>First game: stacks up to +50%</t>
+          <t>x86: 0x44b6d4 (addss xmm0, xmm0)</t>
         </is>
       </c>
     </row>
@@ -11018,12 +11035,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>First game: stacks up to +50%</t>
+          <t>x86: 0x44df6a (addss xmm0, xmm0)</t>
         </is>
       </c>
     </row>
@@ -11033,12 +11050,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>x86: 0x44a736 (flat +10 enmity points)</t>
         </is>
       </c>
     </row>
@@ -11048,12 +11070,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>x86: 0x44a74d (flat -5 enmity points)</t>
         </is>
       </c>
     </row>
@@ -11068,12 +11095,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DT2-2 player test: only five of them count</t>
+          <t>x86: 0x44a114 (mulss 0.10)</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11115,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>x86: 0x44a14d (mulss 0.05)</t>
         </is>
       </c>
     </row>
@@ -11103,12 +11135,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DT2-2 player test: only three of them count</t>
+          <t>x86: 0x449f6a (mulss 0.20)</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11155,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>x86: 0x449fa3 (mulss 0.10)</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11175,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>x86: 0x44d0bd (mulss 0.06)</t>
         </is>
       </c>
     </row>
@@ -11153,7 +11195,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>x86: 0x44d0f4 (mulss 0.03)</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11215,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>x86: 0x44d12b (mulss 0.06)</t>
         </is>
       </c>
     </row>
@@ -11178,17 +11230,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Convert 5% of received damage into TP</t>
+          <t>Damage to TP: 5%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>First game: at least 1 TP, also from poison and traps</t>
+          <t>x86: 0x47e68d (mulss 0.05)</t>
         </is>
       </c>
     </row>
@@ -11203,12 +11255,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e04b (mulss 0.20)</t>
         </is>
       </c>
     </row>
@@ -11223,12 +11275,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e101 (mulss 0.20)</t>
         </is>
       </c>
     </row>
@@ -11243,12 +11295,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e1b7 (mulss 0.20)</t>
         </is>
       </c>
     </row>
@@ -11263,12 +11315,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e26d (mulss 0.20)</t>
         </is>
       </c>
     </row>
@@ -11283,12 +11335,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>First game: magic of that element x1.2, and the weapon attacks with that element</t>
+          <t>x86: 0x44e37d (mulss 0.20)</t>
         </is>
       </c>
     </row>
@@ -12003,12 +12055,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Slash, stab and bash. The DT2-2 wiki lists this one as unknown (-??)</t>
+          <t>x86: 0x4f8b86 (-10 flat resistance)</t>
         </is>
       </c>
     </row>
@@ -12468,17 +12520,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Normal attacks absorb HP (15% of damage)</t>
+          <t>Attacks absorb 15% HP</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>First game: no effect on undead</t>
+          <t>x86: 0x4215c4 (movss 0.15, no undead)</t>
         </is>
       </c>
     </row>
@@ -12488,17 +12540,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Normal attacks absorb HP (50% of damage)</t>
+          <t>Attacks absorb 50% HP</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>First game: no effect on undead</t>
+          <t>x86: 0x42156f (movss 0.50, no undead)</t>
         </is>
       </c>
     </row>
@@ -12508,17 +12560,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Normal attacks absorb TP (5% of damage)</t>
+          <t>Attacks absorb 5% TP</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>First game: no effect on undead</t>
+          <t>x86: 0x42166e (movss 0.05, no undead)</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12580,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Normal attacks absorb TP (20% of damage)</t>
+          <t>Attacks absorb 20% TP</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>First game: no effect on undead</t>
+          <t>x86: 0x421619 (movss 0.20, no undead)</t>
         </is>
       </c>
     </row>
@@ -12548,17 +12600,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+15%</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44bff5 (mulss 0.15)</t>
         </is>
       </c>
     </row>
@@ -12568,17 +12620,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+15%</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
     </row>
@@ -12588,17 +12640,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+15%</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
     </row>
@@ -12608,17 +12660,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+15%</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c1a5 (mulss 0.15)</t>
         </is>
       </c>
     </row>
@@ -12628,17 +12680,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+15%</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
     </row>
@@ -12648,17 +12700,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+15%</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
     </row>
@@ -12668,17 +12720,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+15%</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.2</t>
+          <t>x86: 0x44c01d (mulss 0.15)</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12740,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44bfbb (mulss 0.30)</t>
         </is>
       </c>
     </row>
@@ -12708,17 +12760,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c06f (mulss 0.30)</t>
         </is>
       </c>
     </row>
@@ -12728,17 +12780,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c0ce (mulss 0.30)</t>
         </is>
       </c>
     </row>
@@ -12748,17 +12800,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c16b (mulss 0.30)</t>
         </is>
       </c>
     </row>
@@ -12768,17 +12820,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c1e5 (mulss 0.30)</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12840,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c244 (mulss 0.30)</t>
         </is>
       </c>
     </row>
@@ -12808,17 +12860,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>+40%</t>
+          <t>+30%</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.4</t>
+          <t>x86: 0x44c2a3 (mulss 0.30)</t>
         </is>
       </c>
     </row>
@@ -12833,12 +12885,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>First game: physical damage x1.5</t>
+          <t>x86: 0x44c352 (mulss 0.50)</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12900,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>+100%</t>
+          <t>+60%</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>First game: physical damage x2</t>
+          <t>x86: 0x44c131 (mulss 0.60)</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12925,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>First game: physical damage x2</t>
+          <t>x86: 0x44c32a (+1.0)</t>
         </is>
       </c>
     </row>
@@ -12893,12 +12945,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>dt2-wiki</t>
+          <t>exe-verified</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>First game: physical damage x2</t>
+          <t>x86: 0x44c3ab (+1.0)</t>
         </is>
       </c>
     </row>
@@ -12999,6 +13051,1186 @@
       <c r="E143" t="inlineStr">
         <is>
           <t>Page 105, player test of grand sealbook Heket: 110% / 120% / 130% / 140% with 4 / 3 / 2 / 1 members</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>31</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>+4%</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>x86: 0x44ad18 (mulss 4.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>32</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>x86: 0x44ad52 (addss xmm0, xmm0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>33</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>+4%</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>x86: 0x44b8eb (mulss 4.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>34</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>x86: 0x44b925 (addss xmm0, xmm0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>35</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>+4%</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>x86: 0x44ad91 (mulss 4.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>36</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>x86: 0x44adcb (addss xmm0, xmm0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>39</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>+3%</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>x86: 0x44d67b (mulss 3.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>40</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>+1%</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>x86: 0x44d6bd (addss 1.0 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>41</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>+4%</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>x86: 0x44e5b1 (mulss 4.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>42</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>x86: 0x44e637 (addss xmm1, xmm1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>43</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>+3%</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>x86: 0x44d6f0 (mulss 3.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>44</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>+1%</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>x86: 0x44d742 (addss 1.0 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>45</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>+4%</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>x86: 0x44f357 (mulss 4.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>46</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>+1%</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>x86: 0x44f3f7 (addss 1.0 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>47</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>x86: 0x44f3c0 (mulss 4.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>48</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>-2%</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>x86: 0x44f43f (addss xmm0, xmm0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>53</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>x86: 0x44a185 (mulss 0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>56</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>x86: 0x449fdb (mulss 0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>57</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>x86: 0x44d083 (mulss 0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>61</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>x86: 0x44d166 (mulss 0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>73</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Damage to TP: 10%</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>x86: 0x47e6be (mulss 0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>203</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>x86: 0x44c04d (mulss 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>204</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>205</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>206</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>207</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>208</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>+60%</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>x86: 0x44c02f (mulss 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>209</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>x86: 0x44c3ab (+1.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>211</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Encounter rate -1%</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>x86: 0x4bc812 (-1 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>212</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Encounter rate -2%</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>x86: 0x4bc823 (-2 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>213</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Encounter rate +1%</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>x86: 0x4bc834 (+1 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>214</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Encounter rate +2%</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>x86: 0x4bc843 (+2 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>219</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>x86: 0x44ca0b (mulss 0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>220</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>x86: 0x44ca60 (mulss 0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>246</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>x86: 0x4fd2a7 (mulss 0.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>247</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>x86: 0x4fd31e (mulss 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>248</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>x86: 0x4fd2f8 (mulss 0.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>249</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>-40%</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>x86: 0x4fd31e (mulss 0.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>251</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>252</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>253</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>254</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>255</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>x86: 0x44c485 (mulss 0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>259</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Shop encounters: steps -50%</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>x86: 0x5563b3 (steps counter 50-&gt;25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>261</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>x86: 0x44c8b4 (mulss 0.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>265</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ailment recovery: 2 turns</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>x86: 0x48d202 (ailment threshold 2 turns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>268</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Min Critical rate: 20%</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>x86: 0x44f4c3 (crit floor 20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>272</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Missed spell penalty: 25%</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>x86: 0x44ee4e (75% dmg on miss)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>275</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Double EXP (+100%)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>x86: 0x445a1e (x2.0 EXP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>276</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>x86: 0x558255 (+20 drop rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>280</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>+15%</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>x86: 0x44cd83 (mulss 0.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>290</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>x86: 0x44c8ee (mulss 0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>291</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Mimic chest rate +20%</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>x86: 0x55577a (+20% mimic chance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>296</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4% chance: full HP on turn</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>x86: 0x437d1a (4% full HP on turn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>298</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Chant speed +25%</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>x86: 0x44a380 (+25% chant speed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>302</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>x86: 0x48c04a (mulss 0.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>303</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>+1%</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>x86: 0x48c07e (mulss 0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>304</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>+2%</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>x86: 0x44b533 (mulss 0.02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>305</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>+1%</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>exe-verified</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>x86: 0x44b58e (mulss 0.01)</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -3932,9 +3932,19 @@
           <t>Celebrities</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lightning resistance increased (up to +50).</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>+50</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The wiki gives no figure</t>
+          <t>exe-verified (0x4f92f4)</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{v}% petrifying</t>
+          <t>{v}% petry</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{v}% max HP damage</t>
+          <t>{v}% HP dmg</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3002,7 +3002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3030,470 +3030,867 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Catastrophe</t>
+          <t>Rush Zanber</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inflict a powerful physical attack on one enemy. Inflicts slow ({e122}).</t>
+          <t>Physical damage to an enemy row. [1/7 TP, 10 Pep]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Genocide Rain</t>
+          <t>Catastrophe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rain arrows down upon all enemies across {e147} turns.</t>
+          <t>Powerful physical attack. Inflicts slow ({e122}). [1/3 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wiki: 2 volleys, each attacks every enemy twice a turn for 4 turns</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Divine Punishment!</t>
+          <t>Magical Treasure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deal physical damage to an enemy row. {e119} chance of instakill.</t>
+          <t>Physical damage to an enemy; drop rate UP. [1/3 TP, 5 Pep]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nightmare Fall</t>
+          <t>Genocide Rain</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deal non-elemental damage to all enemies. {e116} chance of sleep.</t>
+          <t>Rain arrows down on all foes across {e147} turns. [1/3 TP, 10 Pep]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Powered-Up Beatdown!</t>
+          <t>Galactic Voice</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inflict one enemy with {e96} bash attacks. {e118} chance of stun.</t>
+          <t>Fully restore party HP, dispel status ailments. [1/5 TP, 5 Pep]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Psychowave</t>
+          <t>Divine Punishment!</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Non-elemental damage to all enemies. DEF and magic defense {e162}.</t>
+          <t>Physical damage to an enemy row. {e119} instakill. [1/4 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The original names DEF only; the data also lowers magic defense (163), as the Japanese text says</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avatara</t>
+          <t>Nightmare Fall</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deal physical damage and {e95} defense-piercing attacks on one enemy.</t>
+          <t>Non-elemental damage to all foes. {e116} sleep. [1/4 TP, 7 Pep]</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gjallarhorn</t>
+          <t>Powered-Up Beatdown!</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Circle Brave ({e161}), Circle Protect ({e162}) and Moon Curtain ({e169}).</t>
+          <t>{e96} bash attacks on one enemy. {e118} stun. [1/3 TP, 5 Pep]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shortened ("all at the same time") to make room</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Suppression Arrow</t>
+          <t>Psychowave</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deal damage through to the back row. {e117} chance to silence/freeze.</t>
+          <t>Non-elem dmg to all foes. DEF &amp; magic DEF {e162}. [1/4 TP, 7 Pep]</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rapid Storm</t>
+          <t>Avatara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Form up: speed {e168} and physical accuracy {e166} for all allies.</t>
+          <t>Physical and {e95} piercing attacks on one foe. [1/2 TP, 15 Pep]</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Evolution</t>
+          <t>Gjallarhorn</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Increase magic attack ({e173}) and critical rate ({e174}) for all allies.</t>
+          <t>Circle Brave/Protect ({e161}), Moon Curtain ({e169}). [1/5 TP, 5 Pep]</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bunker Buster</t>
+          <t>Hell Raiser</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deal damage through to the back row. Physical attack/defense {e161}.</t>
+          <t>Cut enemy row's HP to 25% (no boss effect). [1/3 TP, 7 Pep]</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paralyzing Wind</t>
+          <t>Suppression Arrow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inflict a wind attack against all enemies. {e115} chance of paralysis.</t>
+          <t>Damage to back row. {e117} silence/freeze. [1/3 TP, 7 Pep]</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Daruma-Drop!</t>
+          <t>Rapid Storm</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deal physical damage. {e54} chance to delay the target's next turn.</t>
+          <t>Party speed {e168} and physical accuracy {e166}. [1/7 TP, 5 Pep]</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Testament</t>
+          <t>Holy Blast</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deal physical damage and use Shadow Sew ({e123}) against an enemy row.</t>
+          <t>2,000 direct damage to all foes, dispel buffs. [1/3 TP, 10 Pep]</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brain Burst</t>
+          <t>Evolution</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Physical damage to one enemy. {e113} chance of poison/paralysis/sleep.</t>
+          <t>Allies magic ATK ({e173}) and crit rate ({e174}). [1/4 TP, 5 Pep]</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Happy Banquet</t>
+          <t>Searching Eye</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Increase Pep ({e66}) for the ally whose Pep is the lowest.</t>
+          <t>See the stats of all enemies. [1/9 TP, 3 Pep]</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Hysteric Slap</t>
+          <t>Bunker Buster</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Inflict {e94} bash attacks on an enemy row.</t>
+          <t>Damage to back row. Phys attack/defense {e161}. [1/4 TP, 7 Pep]</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fire of Purgatory</t>
+          <t>Crazy Rush</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Attack one enemy ({e88} damage to Undead, Demons, and Apparitions).</t>
+          <t>Attack an enemy 7 times with wild accuracy. [1/3 TP, 15 Pep]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Same effect and value as God Punch, which says "2x damage"</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Curse Bullet</t>
+          <t>Stampede Heaven</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Waste one enemy and poison it ({e113}) with a rare gun.</t>
+          <t>Attack all enemies twice. [1/4 TP, 10 Pep]</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Beast Blitz</t>
+          <t>Paralyzing Wind</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rough up ({e93} hits) and poison ({e113}) one enemy with dark power.</t>
+          <t>Wind attack to all foes. {e115} paralysis. [1/5 TP, 5 Pep]</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Durchbruch</t>
+          <t>Daruma-Drop!</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Two arrows of light pierce to the back row and may silence ({e117}).</t>
+          <t>Physical damage. {e54} turn delay chance. [1/7 TP, 5 Pep]</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maid Beam</t>
+          <t>Testament</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The deadly Maid Beam pierces to the back row. Petrifying ({e120}).</t>
+          <t>Physical damage &amp; Shadow Sew ({e123}) on a row. [1/3 TP, 5 Pep]</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Feuerkraft</t>
+          <t>Brain Burst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Immolate all enemies and absorb their HP and TP (damage cap {e296}).</t>
+          <t>Physical damage. {e113} poison/paralyze/sleep. [1/4 TP, 7 Pep]</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gold Power</t>
+          <t>Multi-Shadow Clone</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hurl {e433} of your wallet at one enemy (max {e296} damage). No refunds.</t>
+          <t>All allies perform Shadow Clone technique. [1/4 TP, 15 Pep]</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>777 Fever</t>
+          <t>Happy Banquet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dish out paralysis ({e115}) and 7x user level damage to all enemies.</t>
+          <t>Pep {e66} for the ally with the lowest Pep. [1/7 TP, 1 Pep]</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Apocrypha</t>
+          <t>Critical Hits</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Waste one enemy and lower its phys. DEF ({e162}) with a rare gun.</t>
+          <t>Critical attack on all enemies with 100% hit. [1/4 TP, 7 Pep]</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anastasia</t>
+          <t>Hysteric Slap</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Summon the goddess of life to resurrect all allies (HP {e105}).</t>
+          <t>{e94} bash attacks on an enemy row. [1/3 TP, 10 Pep]</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lots Of Guns</t>
+          <t>Fire of Purgatory</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Three firearms in hand, rain lead on random enemies ({e93} hits).</t>
+          <t>Attack one foe ({e88} vs Undead/Demon/Apparition). [1/4 TP, 7 Pep]</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mesmerize</t>
+          <t>Double-Team Attack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cancel enemy chants, dances, songs and dolls by outperforming them.</t>
+          <t>Strike an enemy row from both sides at once. [1/7 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shortened for the battle bar</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Magical Assault</t>
+          <t>Twist and Shout</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Slice a random enemy 2-5 times with friendship power. And swords.</t>
+          <t>Spiral into enemy ranks for a piercing attack. [1/7 TP, 7 Pep]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Shortened for the battle bar</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Elixir</t>
+          <t>Curse Bullet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A secret potion: full HP for the party, debuffs and ailments removed.</t>
+          <t>Waste one enemy and poison it ({e113}). [1/5 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shortened for the battle bar</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gimme Gold</t>
+          <t>Mesmerize</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gain 4x the enemies' gold value at the end of battle. (Min. 100)</t>
+          <t>Cancel enemy chants, dances, songs and dolls. [1/7 TP, 10 Pep]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shortened for the battle bar</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jackpot</t>
+          <t>Jetstream</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deal 77x the user's level in damage to one enemy. Jokers are wild!</t>
+          <t>Dogpile an enemy with three allies in a row. [1/4 TP, 8 Pep]</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shortened for the battle bar</t>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Magical Assault</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Slice a foe 2-5 times with friendship &amp; swords. [1/4 TP, 15 Pep]</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Beast Blitz</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rough up ({e93} hits) and poison ({e113}) one foe. [1/3 TP, 12 Pep]</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>God Punch</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pummel one foe ({e88} vs Undead/Demon/Apparition). [1/5 TP, 10 Pep]</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Durchbruch</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Two light arrows pierce back row; silence ({e117}). [1/5 TP, 12 Pep]</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Maid Beam</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deadly Maid Beam pierces back row. Petrify ({e120}). [1/4 TP, 8 Pep]</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sleep with the Fishes</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lull all enemies to sleep with hypnosis. [1/5 TP, 10 Pep]</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Elixir</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Full party HP; dispel debuffs &amp; ailments. [1/7 TP, 8 Pep]</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Feuerkraft</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Immolate foes, absorb HP/TP ({e296} dmg cap). [1/4 TP, 30 Pep]</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gold Power</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Hurl {e433} wallet at one foe (max {e296} dmg). [1/3 TP, 20 Pep]</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>777 Fever</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Paralysis ({e115}) and 7x Lv dmg to all foes. [1/5 TP, 6 Pep]</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Gimme Gold</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Gain 4x enemies' gold after battle (min 100). [1/7 TP, 20 Pep]</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Death Beam</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Instakill one random combatant, friend or foe. [1/9 TP, 8 Pep]</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Apocrypha</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Waste one enemy and lower phys. DEF ({e162}). [1/4 TP, 12 Pep]</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Anastasia</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Goddess of life resurrects allies (HP {e105}). [1/4 TP, 10 Pep]</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jackpot</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deal 77x user Lv in dmg to a foe. Wild jokers! [All TP, 50 Pep]</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Todokanai Koi</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Damage and likely petrify all enemies by tugging their heartstrings.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Shortened for the battle bar</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Damage and likely petrify all enemies. [1/4 TP, 30 Pep]</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Lots Of Guns</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Three guns rain lead on random foes ({e93} hits). [1/5 TP, 15 Pep]</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>QoL with TP and Pep costs</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B234"/>
+  <dimension ref="A1:B235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8384,6 +8781,18 @@
       <c r="B234" t="inlineStr">
         <is>
           <t>Pointless. Unbearably hot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Dark Cloud</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Roiling mass. Is that a green lady in there?</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -3905,7 +3905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3944,6 +3944,23 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Read in the program: a number below 100 under 15 (0x424766, docs/FORMULAS.md 12.19). The DT2-2 wiki measured about 15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tranquil Song</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Enemy ATK and INT: -10% for 4 turns</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Read in the program (docs/FORMULAS.md 12.19, 0x43749f - 0x437650): on a success every unit of the other side receives an ATK debuff and an INT debuff of -0.1 (effects 41 and 43), asked for 4 turns</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4984,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Turn delay</t>
+          <t>Speed added</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>"Decrease turn delay": the stored value is that decrease</t>
+          <t>Read in the program (docs/FORMULAS.md 12.19, 0x4f72a7): the value is added to the speed of the skill or spell she uses, the figure the boxes show as "Speed: 0.95x". The label "Turn delay" read it as a cut of the delay</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -3905,7 +3905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3929,6 +3929,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Balance_Line</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3944,6 +3949,11 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Read in the program: a number below 100 under 15 (0x424766, docs/FORMULAS.md 12.19). The DT2-2 wiki measured about 15%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Activation rate: 25%</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -4791,7 +4791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5119,6 +5119,23 @@
       <c r="C19" t="inlineStr">
         <is>
           <t>Read in the program (docs/FORMULAS.md 12.19): added to the damage cut against the three races. "Damage taken" is one character too long for the line</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Small Target</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Evasion</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>The name the Balance variant gives the unique skill of Lizerietta (balance_skill_text.xlsx): its value is taken from the hit chance of a blow or a spell on her (effect 338, docs/FORMULAS.md 2.1)</t>
         </is>
       </c>
     </row>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -28,6 +28,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueSkillLabels" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ScriptFixes" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MealBuffs" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DerivedLines" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -705,6 +706,18 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>Meals: the words of a meal sentence that name the buff of each effect type. The build writes after them the level the program gives the buff, read from the executable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DerivedLines</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lines of a skill box whose figure is worked out from what the entry stores, not stored in it; the text check leaves them out (tools/text_checks.py)</t>
         </is>
       </c>
     </row>
@@ -5725,6 +5738,64 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Concentrate</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Interruption rate: -9% -&gt; -17% -&gt; -23% -&gt; -29% -&gt; -33% (L1-5 Max)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1 - 1 / (1 + value), value 0.1 to 0.5 by level</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Balance variant: row X14 of the sheet ExePatches makes the interruption rate of a blow damage / (max HP * 1.5 * (1 + value)) (docs/FORMULAS.md 2.5). The entry stores the value, not the share it takes off</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/mod_project/data_tables/qol_rules.xlsx
+++ b/mod_project/data_tables/qol_rules.xlsx
@@ -5138,17 +5138,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Small Target</t>
+          <t>No Miracles Needed</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evasion</t>
+          <t>Activation rate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The name the Balance variant gives the unique skill of Lizerietta (balance_skill_text.xlsx): its value is taken from the hit chance of a blow or a spell on her (effect 338, docs/FORMULAS.md 2.1)</t>
+          <t>The name the Balance variant gives the unique skill of Lizerietta (balance_skill_text.xlsx): its value is the chance of effect 254, rolled when a hit would take her last HP</t>
         </is>
       </c>
     </row>
